--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486444_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486444_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7163</v>
+        <v>4.4168</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8569</v>
+        <v>6.3724</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.1406</v>
+        <v>-1.9557</v>
       </c>
       <c r="G2" t="n">
         <v>2.632</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8032</v>
+        <v>-0.1027</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6609</v>
+        <v>-0.1454</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1423</v>
+        <v>0.0427</v>
       </c>
       <c r="V2" t="n">
         <v>4.7151</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7083</v>
+        <v>1.4627</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3413</v>
+        <v>0.4039</v>
       </c>
       <c r="F3" t="n">
-        <v>1.367</v>
+        <v>1.0588</v>
       </c>
       <c r="G3" t="n">
         <v>-2.5866</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5776</v>
+        <v>1.3321</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5742</v>
+        <v>0.6369</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0034</v>
+        <v>0.6952</v>
       </c>
       <c r="V3" t="n">
         <v>2.0647</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ALDERETE DIAZ</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1635</v>
+        <v>1.4393</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8016</v>
+        <v>3.1634</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3619</v>
+        <v>-1.7241</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5528</v>
+        <v>1.0978</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8731</v>
+        <v>-3.1295</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3203</v>
+        <v>4.2274</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2825</v>
+        <v>2.5786</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0912</v>
+        <v>-1.2862</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1912</v>
+        <v>3.8648</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8353</v>
+        <v>-1.4808</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9643</v>
+        <v>-1.8433</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1291</v>
+        <v>0.3626</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6288</v>
+        <v>-0.876</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7367</v>
+        <v>-0.1754</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8921</v>
+        <v>-0.7006</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>D. ALDERETE DIAZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2158</v>
+        <v>1.2648</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9399</v>
+        <v>0.0878</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7241</v>
+        <v>1.177</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0978</v>
+        <v>-0.5528</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.1295</v>
+        <v>-0.8731</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2274</v>
+        <v>0.3203</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5786</v>
+        <v>0.2825</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2862</v>
+        <v>0.0912</v>
       </c>
       <c r="L5" t="n">
-        <v>3.8648</v>
+        <v>0.1912</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4808</v>
+        <v>-0.8353</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8433</v>
+        <v>-0.9643</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3626</v>
+        <v>0.1291</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0996</v>
+        <v>0.73</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.399</v>
+        <v>0.0228</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7006</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.767</v>
+        <v>0.9588</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9965</v>
+        <v>2.065</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2294</v>
+        <v>-1.1061</v>
       </c>
       <c r="G6" t="n">
         <v>1.1382</v>
@@ -922,13 +922,13 @@
         <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4968</v>
+        <v>0.6886</v>
       </c>
       <c r="T6" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.1526</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4127</v>
+        <v>0.536</v>
       </c>
       <c r="V6" t="n">
         <v>-1.5204</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ MONTENEGRO</t>
+          <t>S. RODRÍGUEZ RAMOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0562</v>
+        <v>0.4359</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7415</v>
+        <v>-0.3344</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6853</v>
+        <v>0.7703</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5519</v>
+        <v>-0.8275</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0586</v>
+        <v>-2.9654</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4933</v>
+        <v>2.138</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3904</v>
+        <v>1.1203</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3322</v>
+        <v>-1.2711</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0582</v>
+        <v>2.3914</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9422</v>
+        <v>-1.9477</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.3908</v>
+        <v>-1.6943</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5514</v>
+        <v>-0.2534</v>
       </c>
       <c r="P7" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5225</v>
+        <v>2.6101</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.262</v>
+        <v>0.5456</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4386</v>
+        <v>-0.1274</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7006</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.3698</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
         <v>-0.5649999999999999</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. TABOADA HEISKANEN</t>
+          <t>P. HERNANDEZ MONTENEGRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1442</v>
+        <v>-0.0556</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0382</v>
+        <v>2.6297</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1825</v>
+        <v>-2.6853</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1442</v>
+        <v>-1.5519</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1825</v>
+        <v>-1.0586</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0382</v>
+        <v>-0.4933</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0382</v>
+        <v>1.3904</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.3322</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0382</v>
+        <v>0.0582</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1825</v>
+        <v>-2.9422</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1825</v>
+        <v>-2.3908</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.5514</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.3737</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.3269</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.7006</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ RAMOS</t>
+          <t>C. TABOADA HEISKANEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3032</v>
+        <v>-0.1442</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0735</v>
+        <v>0.0382</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7703</v>
+        <v>-0.1825</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8275</v>
+        <v>-0.1442</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.9654</v>
+        <v>-0.1825</v>
       </c>
       <c r="I9" t="n">
-        <v>2.138</v>
+        <v>0.0382</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1203</v>
+        <v>0.0382</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2711</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2.3914</v>
+        <v>0.0382</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9477</v>
+        <v>-0.1825</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6943</v>
+        <v>-0.1825</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2534</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6101</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1935</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8663999999999999</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6729000000000001</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0716</v>
+        <v>-0.6438</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9744</v>
+        <v>-0.6391</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.0047</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8299</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7843</v>
+        <v>-0.3566</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.399</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3854</v>
+        <v>-0.2929</v>
       </c>
       <c r="V10" t="n">
         <v>0.7602</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.202</v>
+        <v>-2.1211</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6518</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8538</v>
+        <v>-2.8847</v>
       </c>
       <c r="G11" t="n">
         <v>0.1595</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9711</v>
+        <v>-0.8902</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.399</v>
+        <v>-0.2872</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.603</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9554</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1394</v>
+        <v>-4.9043</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.676</v>
+        <v>-0.5643</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.4633</v>
+        <v>-4.34</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3123</v>
@@ -1390,13 +1390,13 @@
         <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1543</v>
+        <v>-0.9193</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1935</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9609</v>
+        <v>-0.8376</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8902</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.766699999999998</v>
+        <v>2.1093</v>
       </c>
       <c r="E13" t="n">
-        <v>13.6438</v>
+        <v>13.9862</v>
       </c>
       <c r="F13" t="n">
         <v>-11.877</v>
@@ -1468,13 +1468,13 @@
         <v>14.1379</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5647999999999996</v>
+        <v>-0.2221999999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.08420000000000016</v>
+        <v>0.2584000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4808</v>
+        <v>-0.4806999999999998</v>
       </c>
       <c r="V13" t="n">
         <v>3.934199999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9652</v>
+        <v>5.6313</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7358</v>
+        <v>5.2887</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2295</v>
+        <v>0.3425</v>
       </c>
       <c r="G14" t="n">
         <v>3.9121</v>
@@ -1546,13 +1546,13 @@
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4006</v>
+        <v>0.0667</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3461</v>
+        <v>-0.1009</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0545</v>
+        <v>0.1676</v>
       </c>
       <c r="V14" t="n">
         <v>0.5649999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9928</v>
+        <v>4.26</v>
       </c>
       <c r="E15" t="n">
         <v>4.7028</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.71</v>
+        <v>-0.4428</v>
       </c>
       <c r="G15" t="n">
         <v>2.679</v>
@@ -1624,13 +1624,13 @@
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5515</v>
+        <v>0.8187</v>
       </c>
       <c r="T15" t="n">
         <v>0.2211</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3303</v>
+        <v>0.5975</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7602</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2307</v>
+        <v>1.4864</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9023</v>
+        <v>1.0141</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3284</v>
+        <v>0.4723</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8169</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5173</v>
+        <v>-0.2617</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.399</v>
+        <v>-0.2872</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1184</v>
+        <v>0.0255</v>
       </c>
       <c r="V16" t="n">
         <v>1.695</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2817</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7639</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4822</v>
+        <v>-0.3024</v>
       </c>
       <c r="G17" t="n">
         <v>0.1361</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0.3314</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.399</v>
+        <v>-0.1754</v>
       </c>
       <c r="U17" t="n">
-        <v>0.327</v>
+        <v>0.5068</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1535</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>4.2394</v>
+        <v>4.3512</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.086</v>
+        <v>-3.6904</v>
       </c>
       <c r="G18" t="n">
         <v>3.1311</v>
@@ -1858,13 +1858,13 @@
         <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7177</v>
+        <v>-0.2103</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.399</v>
+        <v>-0.2872</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3187</v>
+        <v>0.0769</v>
       </c>
       <c r="V18" t="n">
         <v>-2.2599</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0262</v>
+        <v>-0.9202</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1</v>
+        <v>1.4442</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1262</v>
+        <v>-2.3644</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6552</v>
+        <v>1.9943</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3498</v>
+        <v>2.6063</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0049</v>
+        <v>-0.612</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6271</v>
+        <v>4.2975</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5506</v>
+        <v>2.5946</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0765</v>
+        <v>1.7029</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2823</v>
+        <v>-2.3031</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2009</v>
+        <v>0.0118</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0814</v>
+        <v>-2.3149</v>
       </c>
       <c r="P19" t="n">
-        <v>0.87</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-3.4801</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8889</v>
+        <v>-0.2397</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4951</v>
+        <v>-0.1334</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3938</v>
+        <v>-0.1064</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.13</v>
+        <v>-0.9347</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>0.7602</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3252</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0968</v>
+        <v>-1.0814</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9972</v>
+        <v>0.9882</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0939</v>
+        <v>-2.0696</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9943</v>
+        <v>-1.6552</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6063</v>
+        <v>0.3498</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.612</v>
+        <v>-2.0049</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2975</v>
+        <v>0.6271</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5946</v>
+        <v>0.5506</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7029</v>
+        <v>0.0765</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3031</v>
+        <v>-2.2823</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0118</v>
+        <v>-0.2009</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.3149</v>
+        <v>-2.0814</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4801</v>
+        <v>-0.2175</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4163</v>
+        <v>0.8337</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5804</v>
+        <v>0.3833</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8359</v>
+        <v>0.4503</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9347</v>
+        <v>-1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7602</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.695</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>A. ZUBIZARRETA ARANBARRI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0601</v>
+        <v>-3.1777</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2777</v>
+        <v>-2.6414</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7824</v>
+        <v>-0.5362</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2906</v>
+        <v>-3.3074</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4258</v>
+        <v>-0.7543</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7164</v>
+        <v>-2.5531</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5431</v>
+        <v>-2.889</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3901</v>
+        <v>-0.6538</v>
       </c>
       <c r="L21" t="n">
-        <v>0.153</v>
+        <v>-2.2352</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8337</v>
+        <v>-0.4184</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9643</v>
+        <v>-0.1004</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8694</v>
+        <v>-0.318</v>
       </c>
       <c r="P21" t="n">
-        <v>-4.1326</v>
+        <v>0.6525</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.7852</v>
+        <v>-0.2175</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1679</v>
+        <v>0.6072</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7691</v>
+        <v>0.4651</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3988</v>
+        <v>0.1421</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1952</v>
+        <v>-1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ZUBIZARRETA ARANBARRI</t>
+          <t>G. MAIZA APECECHEA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0723</v>
+        <v>-3.4904</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4179</v>
+        <v>-1.6451</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6544</v>
+        <v>-1.8453</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3074</v>
+        <v>-2.0048</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7543</v>
+        <v>0.4654</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5531</v>
+        <v>-2.4703</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.889</v>
+        <v>0.3954</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6538</v>
+        <v>0.6998</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.2352</v>
+        <v>-0.3044</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4184</v>
+        <v>-2.4003</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1004</v>
+        <v>-0.2344</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.318</v>
+        <v>-2.1659</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6525</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R22" t="n">
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7125</v>
+        <v>0.2115</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6886</v>
+        <v>-0.0384</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0239</v>
+        <v>0.2499</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.13</v>
+        <v>-0.1745</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. MAIZA APECECHEA</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1352</v>
+        <v>-3.5854</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8687</v>
+        <v>-2.613</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2666</v>
+        <v>-0.9724</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0048</v>
+        <v>-0.2906</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4654</v>
+        <v>0.4258</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.4703</v>
+        <v>-0.7164</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3954</v>
+        <v>1.5431</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6998</v>
+        <v>1.3901</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3044</v>
+        <v>0.153</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4003</v>
+        <v>-1.8337</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2344</v>
+        <v>-0.9643</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1659</v>
+        <v>-0.8694</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5225</v>
+        <v>-4.1326</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3926</v>
+        <v>-4.7852</v>
       </c>
       <c r="R23" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4333</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.262</v>
+        <v>0.4338</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1714</v>
+        <v>0.2088</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1745</v>
+        <v>0.1952</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3904</v>
+        <v>0.1952</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.766700000000001</v>
+        <v>0.4684000000000008</v>
       </c>
       <c r="E24" t="n">
         <v>11.8771</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.6438</v>
+        <v>-11.4087</v>
       </c>
       <c r="G24" t="n">
         <v>3.777700000000001</v>
@@ -2305,7 +2305,7 @@
         <v>16.7759</v>
       </c>
       <c r="L24" t="n">
-        <v>2.111800000000001</v>
+        <v>2.1118</v>
       </c>
       <c r="M24" t="n">
         <v>-15.11</v>
@@ -2326,13 +2326,13 @@
         <v>11.9627</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5648000000000001</v>
+        <v>2.8001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4805999999999999</v>
+        <v>0.4808000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.08389999999999992</v>
+        <v>2.319</v>
       </c>
       <c r="V24" t="n">
         <v>-3.934099999999999</v>
